--- a/CHARMS ME.xlsx
+++ b/CHARMS ME.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7792E5A6-9A7A-4704-84A5-E30081913EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838D3C91-205F-4648-8A89-FE9B74B2C252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{40B4C054-271E-423F-8969-5C137F00DE14}"/>
   </bookViews>
@@ -8011,6 +8011,9 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
     </row>
     <row r="40" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
@@ -8035,6 +8038,9 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
     </row>
     <row r="41" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
@@ -8059,6 +8065,9 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
     </row>
     <row r="42" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
@@ -8083,6 +8092,9 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
     </row>
     <row r="43" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
@@ -8107,6 +8119,9 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
     </row>
     <row r="44" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
@@ -8131,6 +8146,9 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
     </row>
     <row r="45" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
@@ -8155,6 +8173,9 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
     </row>
     <row r="46" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
@@ -8179,6 +8200,9 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
     </row>
     <row r="47" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
@@ -8203,6 +8227,9 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
     </row>
     <row r="48" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
@@ -8227,8 +8254,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+    </row>
+    <row r="49" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>81</v>
       </c>
@@ -8251,8 +8281,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+    </row>
+    <row r="50" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>80</v>
       </c>
@@ -8275,8 +8308,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+    </row>
+    <row r="51" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>79</v>
       </c>
@@ -8299,8 +8335,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+    </row>
+    <row r="52" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>78</v>
       </c>
@@ -8323,8 +8362,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+    </row>
+    <row r="53" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>77</v>
       </c>
@@ -8347,8 +8389,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+    </row>
+    <row r="54" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>76</v>
       </c>
@@ -8371,8 +8416,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+    </row>
+    <row r="55" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>75</v>
       </c>
@@ -8395,8 +8443,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+    </row>
+    <row r="56" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>74</v>
       </c>
@@ -8419,8 +8470,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+    </row>
+    <row r="57" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>73</v>
       </c>
@@ -8443,8 +8497,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+    </row>
+    <row r="58" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>72</v>
       </c>
@@ -8467,8 +8524,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+    </row>
+    <row r="59" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>71</v>
       </c>
@@ -8491,8 +8551,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
+    </row>
+    <row r="60" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>70</v>
       </c>
@@ -8515,8 +8578,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="10"/>
+    </row>
+    <row r="61" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>69</v>
       </c>
@@ -8539,8 +8605,11 @@
         <f t="shared" si="17"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+    </row>
+    <row r="62" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>68</v>
       </c>
@@ -8563,8 +8632,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+    </row>
+    <row r="63" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>67</v>
       </c>
@@ -8587,8 +8659,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
+    </row>
+    <row r="64" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>66</v>
       </c>
@@ -8611,8 +8686,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+    </row>
+    <row r="65" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>65</v>
       </c>
@@ -8635,8 +8713,11 @@
         <f t="shared" si="17"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
+    </row>
+    <row r="66" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>64</v>
       </c>
@@ -8659,8 +8740,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="10"/>
+    </row>
+    <row r="67" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>63</v>
       </c>
@@ -8683,8 +8767,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
+    </row>
+    <row r="68" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>62</v>
       </c>
@@ -8707,8 +8794,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I68" s="10"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="10"/>
+    </row>
+    <row r="69" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>61</v>
       </c>
@@ -8731,8 +8821,11 @@
         <f t="shared" si="17"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="10"/>
+    </row>
+    <row r="70" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>60</v>
       </c>
@@ -8755,8 +8848,11 @@
         <f t="shared" si="17"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I70" s="10"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="10"/>
+    </row>
+    <row r="71" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>59</v>
       </c>
@@ -8779,8 +8875,11 @@
         <f t="shared" ref="G71:G129" si="20">F71+10</f>
         <v>65</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+    </row>
+    <row r="72" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>58</v>
       </c>
@@ -8803,8 +8902,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I72" s="10"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="10"/>
+    </row>
+    <row r="73" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>57</v>
       </c>
@@ -8827,8 +8929,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="10"/>
+    </row>
+    <row r="74" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>56</v>
       </c>
@@ -8851,8 +8956,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="10"/>
+    </row>
+    <row r="75" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>55</v>
       </c>
@@ -8875,8 +8983,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I75" s="10"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="10"/>
+    </row>
+    <row r="76" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>54</v>
       </c>
@@ -8899,8 +9010,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I76" s="10"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="10"/>
+    </row>
+    <row r="77" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>53</v>
       </c>
@@ -8923,8 +9037,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I77" s="10"/>
+      <c r="J77" s="10"/>
+      <c r="K77" s="10"/>
+    </row>
+    <row r="78" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>52</v>
       </c>
@@ -8947,8 +9064,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I78" s="10"/>
+      <c r="J78" s="10"/>
+      <c r="K78" s="10"/>
+    </row>
+    <row r="79" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>51</v>
       </c>
@@ -8971,8 +9091,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I79" s="10"/>
+      <c r="J79" s="10"/>
+      <c r="K79" s="10"/>
+    </row>
+    <row r="80" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>50</v>
       </c>
@@ -8995,8 +9118,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I80" s="10"/>
+      <c r="J80" s="10"/>
+      <c r="K80" s="10"/>
+    </row>
+    <row r="81" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>49</v>
       </c>
@@ -9019,8 +9145,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+    </row>
+    <row r="82" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>48</v>
       </c>
@@ -9043,8 +9172,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+      <c r="K82" s="10"/>
+    </row>
+    <row r="83" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>47</v>
       </c>
@@ -9067,8 +9199,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I83" s="10"/>
+      <c r="J83" s="10"/>
+      <c r="K83" s="10"/>
+    </row>
+    <row r="84" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46</v>
       </c>
@@ -9091,8 +9226,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I84" s="10"/>
+      <c r="J84" s="10"/>
+      <c r="K84" s="10"/>
+    </row>
+    <row r="85" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>45</v>
       </c>
@@ -9115,8 +9253,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I85" s="10"/>
+      <c r="J85" s="10"/>
+      <c r="K85" s="10"/>
+    </row>
+    <row r="86" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>44</v>
       </c>
@@ -9139,8 +9280,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I86" s="10"/>
+      <c r="J86" s="10"/>
+      <c r="K86" s="10"/>
+    </row>
+    <row r="87" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>43</v>
       </c>
@@ -9163,8 +9307,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I87" s="10"/>
+      <c r="J87" s="10"/>
+      <c r="K87" s="10"/>
+    </row>
+    <row r="88" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>42</v>
       </c>
@@ -9187,8 +9334,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I88" s="10"/>
+      <c r="J88" s="10"/>
+      <c r="K88" s="10"/>
+    </row>
+    <row r="89" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>41</v>
       </c>
@@ -9211,8 +9361,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I89" s="10"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="10"/>
+    </row>
+    <row r="90" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>40</v>
       </c>
@@ -9235,8 +9388,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I90" s="10"/>
+      <c r="J90" s="10"/>
+      <c r="K90" s="10"/>
+    </row>
+    <row r="91" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>39</v>
       </c>
@@ -9259,8 +9415,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I91" s="10"/>
+      <c r="J91" s="10"/>
+      <c r="K91" s="10"/>
+    </row>
+    <row r="92" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>38</v>
       </c>
@@ -9283,8 +9442,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I92" s="10"/>
+      <c r="J92" s="10"/>
+      <c r="K92" s="10"/>
+    </row>
+    <row r="93" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>37</v>
       </c>
@@ -9307,8 +9469,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I93" s="10"/>
+      <c r="J93" s="10"/>
+      <c r="K93" s="10"/>
+    </row>
+    <row r="94" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>36</v>
       </c>
@@ -9331,8 +9496,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I94" s="10"/>
+      <c r="J94" s="10"/>
+      <c r="K94" s="10"/>
+    </row>
+    <row r="95" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>35</v>
       </c>
@@ -9355,8 +9523,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+    </row>
+    <row r="96" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>34</v>
       </c>
@@ -9379,8 +9550,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I96" s="10"/>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+    </row>
+    <row r="97" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>33</v>
       </c>
@@ -9403,8 +9577,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I97" s="10"/>
+      <c r="J97" s="10"/>
+      <c r="K97" s="10"/>
+    </row>
+    <row r="98" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>32</v>
       </c>
@@ -9427,8 +9604,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I98" s="10"/>
+      <c r="J98" s="10"/>
+      <c r="K98" s="10"/>
+    </row>
+    <row r="99" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>31</v>
       </c>
@@ -9451,8 +9631,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I99" s="10"/>
+      <c r="J99" s="10"/>
+      <c r="K99" s="10"/>
+    </row>
+    <row r="100" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>30</v>
       </c>
@@ -9475,8 +9658,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I100" s="10"/>
+      <c r="J100" s="10"/>
+      <c r="K100" s="10"/>
+    </row>
+    <row r="101" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>29</v>
       </c>
@@ -9499,8 +9685,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I101" s="10"/>
+      <c r="J101" s="10"/>
+      <c r="K101" s="10"/>
+    </row>
+    <row r="102" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>28</v>
       </c>
@@ -9523,8 +9712,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I102" s="10"/>
+      <c r="J102" s="10"/>
+      <c r="K102" s="10"/>
+    </row>
+    <row r="103" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>27</v>
       </c>
@@ -9547,8 +9739,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I103" s="10"/>
+      <c r="J103" s="10"/>
+      <c r="K103" s="10"/>
+    </row>
+    <row r="104" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>26</v>
       </c>
@@ -9571,8 +9766,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I104" s="10"/>
+      <c r="J104" s="10"/>
+      <c r="K104" s="10"/>
+    </row>
+    <row r="105" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>25</v>
       </c>
@@ -9595,8 +9793,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I105" s="10"/>
+      <c r="J105" s="10"/>
+      <c r="K105" s="10"/>
+    </row>
+    <row r="106" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>24</v>
       </c>
@@ -9619,8 +9820,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I106" s="10"/>
+      <c r="J106" s="10"/>
+      <c r="K106" s="10"/>
+    </row>
+    <row r="107" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>23</v>
       </c>
@@ -9643,8 +9847,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I107" s="10"/>
+      <c r="J107" s="10"/>
+      <c r="K107" s="10"/>
+    </row>
+    <row r="108" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>22</v>
       </c>
@@ -9667,8 +9874,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I108" s="10"/>
+      <c r="J108" s="10"/>
+      <c r="K108" s="10"/>
+    </row>
+    <row r="109" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>21</v>
       </c>
@@ -9691,8 +9901,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I109" s="10"/>
+      <c r="J109" s="10"/>
+      <c r="K109" s="10"/>
+    </row>
+    <row r="110" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>20</v>
       </c>
@@ -9715,8 +9928,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I110" s="10"/>
+      <c r="J110" s="10"/>
+      <c r="K110" s="10"/>
+    </row>
+    <row r="111" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>19</v>
       </c>
@@ -9739,8 +9955,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I111" s="10"/>
+      <c r="J111" s="10"/>
+      <c r="K111" s="10"/>
+    </row>
+    <row r="112" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>18</v>
       </c>
@@ -9763,8 +9982,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I112" s="10"/>
+      <c r="J112" s="10"/>
+      <c r="K112" s="10"/>
+    </row>
+    <row r="113" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>17</v>
       </c>
@@ -9787,8 +10009,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I113" s="10"/>
+      <c r="J113" s="10"/>
+      <c r="K113" s="10"/>
+    </row>
+    <row r="114" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>16</v>
       </c>
@@ -9811,8 +10036,11 @@
         <f t="shared" si="20"/>
         <v>70</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I114" s="10"/>
+      <c r="J114" s="10"/>
+      <c r="K114" s="10"/>
+    </row>
+    <row r="115" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>15</v>
       </c>
@@ -9835,8 +10063,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I115" s="10"/>
+      <c r="J115" s="10"/>
+      <c r="K115" s="10"/>
+    </row>
+    <row r="116" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>14</v>
       </c>
@@ -9859,8 +10090,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I116" s="10"/>
+      <c r="J116" s="10"/>
+      <c r="K116" s="10"/>
+    </row>
+    <row r="117" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>13</v>
       </c>
@@ -9883,8 +10117,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I117" s="10"/>
+      <c r="J117" s="10"/>
+      <c r="K117" s="10"/>
+    </row>
+    <row r="118" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>12</v>
       </c>
@@ -9907,8 +10144,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I118" s="10"/>
+      <c r="J118" s="10"/>
+      <c r="K118" s="10"/>
+    </row>
+    <row r="119" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>11</v>
       </c>
@@ -9931,8 +10171,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I119" s="10"/>
+      <c r="J119" s="10"/>
+      <c r="K119" s="10"/>
+    </row>
+    <row r="120" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>10</v>
       </c>
@@ -9955,8 +10198,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I120" s="10"/>
+      <c r="J120" s="10"/>
+      <c r="K120" s="10"/>
+    </row>
+    <row r="121" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>9</v>
       </c>
@@ -9979,8 +10225,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I121" s="10"/>
+      <c r="J121" s="10"/>
+      <c r="K121" s="10"/>
+    </row>
+    <row r="122" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>8</v>
       </c>
@@ -10003,8 +10252,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I122" s="10"/>
+      <c r="J122" s="10"/>
+      <c r="K122" s="10"/>
+    </row>
+    <row r="123" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>7</v>
       </c>
@@ -10027,8 +10279,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I123" s="10"/>
+      <c r="J123" s="10"/>
+      <c r="K123" s="10"/>
+    </row>
+    <row r="124" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>6</v>
       </c>
@@ -10051,8 +10306,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I124" s="10"/>
+      <c r="J124" s="10"/>
+      <c r="K124" s="10"/>
+    </row>
+    <row r="125" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>5</v>
       </c>
@@ -10075,8 +10333,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I125" s="10"/>
+      <c r="J125" s="10"/>
+      <c r="K125" s="10"/>
+    </row>
+    <row r="126" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>4</v>
       </c>
@@ -10099,8 +10360,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I126" s="10"/>
+      <c r="J126" s="10"/>
+      <c r="K126" s="10"/>
+    </row>
+    <row r="127" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>3</v>
       </c>
@@ -10123,8 +10387,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I127" s="10"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="10"/>
+    </row>
+    <row r="128" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>2</v>
       </c>
@@ -10147,8 +10414,11 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I128" s="10"/>
+      <c r="J128" s="10"/>
+      <c r="K128" s="10"/>
+    </row>
+    <row r="129" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>1</v>
       </c>
@@ -10171,6 +10441,9 @@
         <f t="shared" si="20"/>
         <v>65</v>
       </c>
+      <c r="I129" s="10"/>
+      <c r="J129" s="10"/>
+      <c r="K129" s="10"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
